--- a/load_and_merge_scripts/data/operational.xlsx
+++ b/load_and_merge_scripts/data/operational.xlsx
@@ -2,20 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="Raf9ac2c17964443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TenantMetadataDiscoveryScope" sheetId="2" r:id="R735c6a5e9e224692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConnectionLocation" sheetId="3" r:id="R60a9a6484af6401a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConnectionValue" sheetId="4" r:id="R0ae8d9bb16d44e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Object" sheetId="5" r:id="R3dcf2bcf8fc848c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attribute" sheetId="6" r:id="R17bfd8839a464a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IngestionObjectMapping" sheetId="7" r:id="Rb28b38a2c7e94d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IngestionAttributeMapping" sheetId="8" r:id="Rc7b0abf298454b56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopyGroup" sheetId="9" r:id="Re66d06c39adc4a1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MemberGroup" sheetId="10" r:id="R4f8de82a31c8415c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopyGroupControl" sheetId="11" r:id="R002dfc9db4874caf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy" sheetId="12" r:id="R3a102488ca8a459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessGroup" sheetId="13" r:id="R05c928ed08494c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process" sheetId="14" r:id="R2808b4f6515d4321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" r:id="Re5173367f5484108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConnectionLocation" sheetId="3" r:id="R1bd960474817494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ConnectionValue" sheetId="4" r:id="R9fc63bff19e747fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Object" sheetId="5" r:id="R42d8b82cd54043fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attribute" sheetId="6" r:id="R7189351a89d04d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IngestionObjectMapping" sheetId="7" r:id="R62d2a6faec3c4e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IngestionAttributeMapping" sheetId="8" r:id="Rb630c1ec9cb24499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopyGroup" sheetId="9" r:id="R838b5a5ee7b34166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MemberGroup" sheetId="10" r:id="R1573e88054364823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopyGroupControl" sheetId="11" r:id="Rad83a3fb64ee444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy" sheetId="12" r:id="R782ac743620d4ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessGroup" sheetId="13" r:id="Rc1766f4539b84dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Process" sheetId="14" r:id="Rc1e108f7aeec4254"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +54,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -80,6 +79,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF9E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF334155"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F766E"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -244,7 +253,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="62">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -369,6 +378,18 @@
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -662,224 +683,214 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="43" t="n">
-        <x:v>270</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B11" s="35" t="str">
-        <x:v>TenantMetadataDiscoveryScope</x:v>
+        <x:v>ConnectionLocation</x:v>
       </x:c>
       <x:c r="C11" s="35" t="str">
-        <x:v>core.tenant_metadata_discovery_scope</x:v>
+        <x:v>core.connection_location</x:v>
       </x:c>
       <x:c r="D11" s="35" t="str">
-        <x:v>scope_tenant_code, connection_tenant_code, connection_system_code, connection_code, zone_code, object_schema</x:v>
+        <x:v>tenant_code, system_code, connection_code, location_type_name, environment_code, connection_location_storage_account, connection_location_secret_reference, connection_location_container, connection_location_path</x:v>
       </x:c>
       <x:c r="E11" s="36" t="str">
-        <x:v>scope_tenant_code, connection_tenant_code, connection_system_code, connection_code, zone_code, object_schema</x:v>
+        <x:v>tenant_code, system_code, connection_code, location_type_name, environment_code</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="44" t="n">
-        <x:v>280</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B12" s="38" t="str">
-        <x:v>ConnectionLocation</x:v>
+        <x:v>ConnectionValue</x:v>
       </x:c>
       <x:c r="C12" s="38" t="str">
-        <x:v>core.connection_location</x:v>
+        <x:v>core.connection_value</x:v>
       </x:c>
       <x:c r="D12" s="38" t="str">
-        <x:v>tenant_code, system_code, connection_code, location_type_name, environment_code, connection_location_storage_account, connection_location_secret_reference, connection_location_container, connection_location_path</x:v>
+        <x:v>tenant_code, system_code, connection_code, environment_code, connection_parameter_code</x:v>
       </x:c>
       <x:c r="E12" s="39" t="str">
-        <x:v>tenant_code, system_code, connection_code, location_type_name, environment_code</x:v>
+        <x:v>tenant_code, system_code, connection_code, environment_code, connection_parameter_code</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="44" t="n">
-        <x:v>290</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B13" s="38" t="str">
-        <x:v>ConnectionValue</x:v>
+        <x:v>Object</x:v>
       </x:c>
       <x:c r="C13" s="38" t="str">
-        <x:v>core.connection_value</x:v>
+        <x:v>core.object</x:v>
       </x:c>
       <x:c r="D13" s="38" t="str">
-        <x:v>tenant_code, system_code, connection_code, environment_code, connection_parameter_code</x:v>
+        <x:v>tenant_code, source_tenant_code, system_code, connection_code, object_schema, object_name, object_type_code, zone_code</x:v>
       </x:c>
       <x:c r="E13" s="39" t="str">
-        <x:v>tenant_code, system_code, connection_code, environment_code, connection_parameter_code</x:v>
+        <x:v>tenant_code, system_code, connection_code, object_schema, object_name</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="44" t="n">
-        <x:v>300</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B14" s="38" t="str">
-        <x:v>Object</x:v>
+        <x:v>Attribute</x:v>
       </x:c>
       <x:c r="C14" s="38" t="str">
-        <x:v>core.object</x:v>
+        <x:v>core.attribute</x:v>
       </x:c>
       <x:c r="D14" s="38" t="str">
-        <x:v>tenant_code, system_code, connection_code, object_schema, object_name, object_type_code, zone_code</x:v>
+        <x:v>tenant_code, system_code, connection_code, object_schema, object_name, attribute_name, attribute_ordinal_position, attribute_data_type</x:v>
       </x:c>
       <x:c r="E14" s="39" t="str">
-        <x:v>tenant_code, system_code, connection_code, object_schema, object_name</x:v>
+        <x:v>tenant_code, system_code, connection_code, object_schema, object_name, attribute_name</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="44" t="n">
-        <x:v>310</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B15" s="38" t="str">
-        <x:v>Attribute</x:v>
+        <x:v>IngestionObjectMapping</x:v>
       </x:c>
       <x:c r="C15" s="38" t="str">
-        <x:v>core.attribute</x:v>
+        <x:v>core.ingestion_object_mapping</x:v>
       </x:c>
       <x:c r="D15" s="38" t="str">
-        <x:v>tenant_code, system_code, connection_code, object_schema, object_name, attribute_name, attribute_ordinal_position, attribute_data_type</x:v>
+        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name</x:v>
       </x:c>
       <x:c r="E15" s="39" t="str">
-        <x:v>tenant_code, system_code, connection_code, object_schema, object_name, attribute_name</x:v>
+        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="44" t="n">
-        <x:v>320</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B16" s="38" t="str">
-        <x:v>IngestionObjectMapping</x:v>
+        <x:v>IngestionAttributeMapping</x:v>
       </x:c>
       <x:c r="C16" s="38" t="str">
-        <x:v>core.ingestion_object_mapping</x:v>
+        <x:v>core.ingestion_attribute_mapping</x:v>
       </x:c>
       <x:c r="D16" s="38" t="str">
-        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name</x:v>
+        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, source_attribute_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name, target_attribute_name</x:v>
       </x:c>
       <x:c r="E16" s="39" t="str">
-        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name</x:v>
+        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, source_attribute_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name, target_attribute_name</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="44" t="n">
-        <x:v>330</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B17" s="38" t="str">
-        <x:v>IngestionAttributeMapping</x:v>
+        <x:v>CopyGroup</x:v>
       </x:c>
       <x:c r="C17" s="38" t="str">
-        <x:v>core.ingestion_attribute_mapping</x:v>
+        <x:v>core.copy_group</x:v>
       </x:c>
       <x:c r="D17" s="38" t="str">
-        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, source_attribute_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name, target_attribute_name</x:v>
+        <x:v>tenant_code, system_code, copy_group_name</x:v>
       </x:c>
       <x:c r="E17" s="39" t="str">
-        <x:v>source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, source_attribute_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name, target_attribute_name</x:v>
+        <x:v>tenant_code, system_code, copy_group_name</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="44" t="n">
-        <x:v>340</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B18" s="38" t="str">
-        <x:v>CopyGroup</x:v>
+        <x:v>MemberGroup</x:v>
       </x:c>
       <x:c r="C18" s="38" t="str">
-        <x:v>core.copy_group</x:v>
+        <x:v>core.member_group</x:v>
       </x:c>
       <x:c r="D18" s="38" t="str">
-        <x:v>tenant_code, system_code, copy_group_name</x:v>
+        <x:v>tenant_code, system_code, member_group_name</x:v>
       </x:c>
       <x:c r="E18" s="39" t="str">
-        <x:v>tenant_code, system_code, copy_group_name</x:v>
+        <x:v>tenant_code, system_code, member_group_name</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="44" t="n">
-        <x:v>350</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B19" s="38" t="str">
-        <x:v>MemberGroup</x:v>
+        <x:v>CopyGroupControl</x:v>
       </x:c>
       <x:c r="C19" s="38" t="str">
-        <x:v>core.member_group</x:v>
+        <x:v>core.copy_group_control</x:v>
       </x:c>
       <x:c r="D19" s="38" t="str">
-        <x:v>tenant_code, system_code, member_group_name</x:v>
+        <x:v>tenant_code, system_code, copy_group_name</x:v>
       </x:c>
       <x:c r="E19" s="39" t="str">
-        <x:v>tenant_code, system_code, member_group_name</x:v>
+        <x:v>tenant_code, system_code, copy_group_name, member_group_name</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="44" t="n">
-        <x:v>360</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B20" s="38" t="str">
-        <x:v>CopyGroupControl</x:v>
+        <x:v>Copy</x:v>
       </x:c>
       <x:c r="C20" s="38" t="str">
-        <x:v>core.copy_group_control</x:v>
+        <x:v>core.copy</x:v>
       </x:c>
       <x:c r="D20" s="38" t="str">
-        <x:v>tenant_code, system_code, copy_group_name</x:v>
+        <x:v>tenant_code, system_code, copy_group_name, source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name, copy_source_order, source_data_operation_name, target_data_operation_name</x:v>
       </x:c>
       <x:c r="E20" s="39" t="str">
-        <x:v>tenant_code, system_code, copy_group_name, member_group_name</x:v>
+        <x:v>tenant_code, system_code, copy_group_name, source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="44" t="n">
-        <x:v>370</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B21" s="38" t="str">
-        <x:v>Copy</x:v>
+        <x:v>ProcessGroup</x:v>
       </x:c>
       <x:c r="C21" s="38" t="str">
-        <x:v>core.copy</x:v>
+        <x:v>core.process_group</x:v>
       </x:c>
       <x:c r="D21" s="38" t="str">
-        <x:v>tenant_code, system_code, copy_group_name, source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name, copy_source_order, source_data_operation_name, target_data_operation_name</x:v>
+        <x:v>tenant_code, system_code, zone_code, process_group_name, copy_group_name</x:v>
       </x:c>
       <x:c r="E21" s="39" t="str">
-        <x:v>tenant_code, system_code, copy_group_name, source_tenant_code, source_system_code, source_connection_code, source_object_schema, source_object_name, target_tenant_code, target_system_code, target_connection_code, target_object_schema, target_object_name</x:v>
+        <x:v>tenant_code, system_code, zone_code, process_group_name</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="44" t="n">
-        <x:v>380</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B22" s="38" t="str">
-        <x:v>ProcessGroup</x:v>
+        <x:v>Process</x:v>
       </x:c>
       <x:c r="C22" s="38" t="str">
-        <x:v>core.process_group</x:v>
+        <x:v>core.process</x:v>
       </x:c>
       <x:c r="D22" s="38" t="str">
-        <x:v>tenant_code, system_code, zone_code, process_group_name, copy_group_name</x:v>
+        <x:v>process_group_tenant_code, process_group_system_code, process_group_zone_code, process_group_name, object_tenant_code, object_system_code, object_connection_code, object_schema, object_name, process_execution_order, process_location, process_executable, process_type_name</x:v>
       </x:c>
       <x:c r="E22" s="39" t="str">
-        <x:v>tenant_code, system_code, zone_code, process_group_name</x:v>
+        <x:v>process_group_tenant_code, process_group_system_code, process_group_zone_code, process_group_name, process_execution_order, process_location, process_executable</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="45" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="B23" s="41" t="str">
-        <x:v>Process</x:v>
-      </x:c>
-      <x:c r="C23" s="41" t="str">
-        <x:v>core.process</x:v>
-      </x:c>
-      <x:c r="D23" s="41" t="str">
-        <x:v>process_group_tenant_code, process_group_system_code, process_group_zone_code, process_group_name, object_tenant_code, object_system_code, object_connection_code, object_schema, object_name, process_execution_order, process_location, process_executable, process_type_name</x:v>
-      </x:c>
-      <x:c r="E23" s="42" t="str">
-        <x:v>process_group_tenant_code, process_group_system_code, process_group_zone_code, process_group_name, process_execution_order, process_location, process_executable</x:v>
-      </x:c>
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -890,1550 +901,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="52" t="str">
-        <x:v>tenant_code</x:v>
-      </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>system_code</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>member_group_name</x:v>
-      </x:c>
-      <x:c r="D1" s="57" t="str">
-        <x:v>member_group_description</x:v>
-      </x:c>
-      <x:c r="E1" s="57" t="str">
-        <x:v>member_group_initial_load_date</x:v>
-      </x:c>
-      <x:c r="F1" s="57" t="str">
-        <x:v>is_active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="47"/>
-      <x:c r="B2" s="48"/>
-      <x:c r="C2" s="48"/>
-      <x:c r="D2" s="48"/>
-      <x:c r="E2" s="58"/>
-      <x:c r="F2" s="49"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="E3" s="59"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="E4" s="59"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="E5" s="59"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="E6" s="59"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="E7" s="59"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="E8" s="59"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="E9" s="59"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="E10" s="59"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="E11" s="59"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="E12" s="59"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="E13" s="59"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="E14" s="59"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="E15" s="59"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="E16" s="59"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="E17" s="59"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="E18" s="59"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="E19" s="59"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="E20" s="59"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="E21" s="59"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="E22" s="59"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="E23" s="59"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="E24" s="59"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="E25" s="59"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="E26" s="59"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="E27" s="59"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="E28" s="59"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="E29" s="59"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="E30" s="59"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="E31" s="59"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="E32" s="59"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="E33" s="59"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="E34" s="59"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="E35" s="59"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="E36" s="59"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="E37" s="59"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="E38" s="59"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="E39" s="59"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="E40" s="59"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="E41" s="59"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="E42" s="59"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="E43" s="59"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="E44" s="59"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="E45" s="59"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="E46" s="59"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="E47" s="59"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="E48" s="59"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="E49" s="59"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="E50" s="59"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="E51" s="59"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="E52" s="59"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="E53" s="59"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="E54" s="59"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="E55" s="59"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="E56" s="59"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="E57" s="59"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="E58" s="59"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="E59" s="59"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="E60" s="59"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="E61" s="59"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="E62" s="59"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="E63" s="59"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="E64" s="59"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="E65" s="59"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="E66" s="59"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="E67" s="59"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="E68" s="59"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="E69" s="59"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="E70" s="59"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="E71" s="59"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="E72" s="59"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="E73" s="59"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="E74" s="59"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="E75" s="59"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="E76" s="59"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="E77" s="59"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="E78" s="59"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="E79" s="59"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="E80" s="59"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="E81" s="59"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="E82" s="59"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="E83" s="59"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="E84" s="59"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="E85" s="59"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="E86" s="59"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="E87" s="59"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="E88" s="59"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="E89" s="59"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="E90" s="59"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="E91" s="59"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="E92" s="59"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="E93" s="59"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="E94" s="59"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="E95" s="59"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="E96" s="59"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="E97" s="59"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="E98" s="59"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="E99" s="59"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="E100" s="59"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="E101" s="59"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="E102" s="59"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="E103" s="59"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="E104" s="59"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="E105" s="59"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="E106" s="59"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="E107" s="59"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="E108" s="59"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="E109" s="59"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="E110" s="59"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="E111" s="59"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="E112" s="59"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="E113" s="59"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="E114" s="59"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="E115" s="59"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="E116" s="59"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="E117" s="59"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="E118" s="59"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="E119" s="59"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="E120" s="59"/>
-    </x:row>
-    <x:row r="121">
-      <x:c r="E121" s="59"/>
-    </x:row>
-    <x:row r="122">
-      <x:c r="E122" s="59"/>
-    </x:row>
-    <x:row r="123">
-      <x:c r="E123" s="59"/>
-    </x:row>
-    <x:row r="124">
-      <x:c r="E124" s="59"/>
-    </x:row>
-    <x:row r="125">
-      <x:c r="E125" s="59"/>
-    </x:row>
-    <x:row r="126">
-      <x:c r="E126" s="59"/>
-    </x:row>
-    <x:row r="127">
-      <x:c r="E127" s="59"/>
-    </x:row>
-    <x:row r="128">
-      <x:c r="E128" s="59"/>
-    </x:row>
-    <x:row r="129">
-      <x:c r="E129" s="59"/>
-    </x:row>
-    <x:row r="130">
-      <x:c r="E130" s="59"/>
-    </x:row>
-    <x:row r="131">
-      <x:c r="E131" s="59"/>
-    </x:row>
-    <x:row r="132">
-      <x:c r="E132" s="59"/>
-    </x:row>
-    <x:row r="133">
-      <x:c r="E133" s="59"/>
-    </x:row>
-    <x:row r="134">
-      <x:c r="E134" s="59"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="E135" s="59"/>
-    </x:row>
-    <x:row r="136">
-      <x:c r="E136" s="59"/>
-    </x:row>
-    <x:row r="137">
-      <x:c r="E137" s="59"/>
-    </x:row>
-    <x:row r="138">
-      <x:c r="E138" s="59"/>
-    </x:row>
-    <x:row r="139">
-      <x:c r="E139" s="59"/>
-    </x:row>
-    <x:row r="140">
-      <x:c r="E140" s="59"/>
-    </x:row>
-    <x:row r="141">
-      <x:c r="E141" s="59"/>
-    </x:row>
-    <x:row r="142">
-      <x:c r="E142" s="59"/>
-    </x:row>
-    <x:row r="143">
-      <x:c r="E143" s="59"/>
-    </x:row>
-    <x:row r="144">
-      <x:c r="E144" s="59"/>
-    </x:row>
-    <x:row r="145">
-      <x:c r="E145" s="59"/>
-    </x:row>
-    <x:row r="146">
-      <x:c r="E146" s="59"/>
-    </x:row>
-    <x:row r="147">
-      <x:c r="E147" s="59"/>
-    </x:row>
-    <x:row r="148">
-      <x:c r="E148" s="59"/>
-    </x:row>
-    <x:row r="149">
-      <x:c r="E149" s="59"/>
-    </x:row>
-    <x:row r="150">
-      <x:c r="E150" s="59"/>
-    </x:row>
-    <x:row r="151">
-      <x:c r="E151" s="59"/>
-    </x:row>
-    <x:row r="152">
-      <x:c r="E152" s="59"/>
-    </x:row>
-    <x:row r="153">
-      <x:c r="E153" s="59"/>
-    </x:row>
-    <x:row r="154">
-      <x:c r="E154" s="59"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="E155" s="59"/>
-    </x:row>
-    <x:row r="156">
-      <x:c r="E156" s="59"/>
-    </x:row>
-    <x:row r="157">
-      <x:c r="E157" s="59"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="E158" s="59"/>
-    </x:row>
-    <x:row r="159">
-      <x:c r="E159" s="59"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="E160" s="59"/>
-    </x:row>
-    <x:row r="161">
-      <x:c r="E161" s="59"/>
-    </x:row>
-    <x:row r="162">
-      <x:c r="E162" s="59"/>
-    </x:row>
-    <x:row r="163">
-      <x:c r="E163" s="59"/>
-    </x:row>
-    <x:row r="164">
-      <x:c r="E164" s="59"/>
-    </x:row>
-    <x:row r="165">
-      <x:c r="E165" s="59"/>
-    </x:row>
-    <x:row r="166">
-      <x:c r="E166" s="59"/>
-    </x:row>
-    <x:row r="167">
-      <x:c r="E167" s="59"/>
-    </x:row>
-    <x:row r="168">
-      <x:c r="E168" s="59"/>
-    </x:row>
-    <x:row r="169">
-      <x:c r="E169" s="59"/>
-    </x:row>
-    <x:row r="170">
-      <x:c r="E170" s="59"/>
-    </x:row>
-    <x:row r="171">
-      <x:c r="E171" s="59"/>
-    </x:row>
-    <x:row r="172">
-      <x:c r="E172" s="59"/>
-    </x:row>
-    <x:row r="173">
-      <x:c r="E173" s="59"/>
-    </x:row>
-    <x:row r="174">
-      <x:c r="E174" s="59"/>
-    </x:row>
-    <x:row r="175">
-      <x:c r="E175" s="59"/>
-    </x:row>
-    <x:row r="176">
-      <x:c r="E176" s="59"/>
-    </x:row>
-    <x:row r="177">
-      <x:c r="E177" s="59"/>
-    </x:row>
-    <x:row r="178">
-      <x:c r="E178" s="59"/>
-    </x:row>
-    <x:row r="179">
-      <x:c r="E179" s="59"/>
-    </x:row>
-    <x:row r="180">
-      <x:c r="E180" s="59"/>
-    </x:row>
-    <x:row r="181">
-      <x:c r="E181" s="59"/>
-    </x:row>
-    <x:row r="182">
-      <x:c r="E182" s="59"/>
-    </x:row>
-    <x:row r="183">
-      <x:c r="E183" s="59"/>
-    </x:row>
-    <x:row r="184">
-      <x:c r="E184" s="59"/>
-    </x:row>
-    <x:row r="185">
-      <x:c r="E185" s="59"/>
-    </x:row>
-    <x:row r="186">
-      <x:c r="E186" s="59"/>
-    </x:row>
-    <x:row r="187">
-      <x:c r="E187" s="59"/>
-    </x:row>
-    <x:row r="188">
-      <x:c r="E188" s="59"/>
-    </x:row>
-    <x:row r="189">
-      <x:c r="E189" s="59"/>
-    </x:row>
-    <x:row r="190">
-      <x:c r="E190" s="59"/>
-    </x:row>
-    <x:row r="191">
-      <x:c r="E191" s="59"/>
-    </x:row>
-    <x:row r="192">
-      <x:c r="E192" s="59"/>
-    </x:row>
-    <x:row r="193">
-      <x:c r="E193" s="59"/>
-    </x:row>
-    <x:row r="194">
-      <x:c r="E194" s="59"/>
-    </x:row>
-    <x:row r="195">
-      <x:c r="E195" s="59"/>
-    </x:row>
-    <x:row r="196">
-      <x:c r="E196" s="59"/>
-    </x:row>
-    <x:row r="197">
-      <x:c r="E197" s="59"/>
-    </x:row>
-    <x:row r="198">
-      <x:c r="E198" s="59"/>
-    </x:row>
-    <x:row r="199">
-      <x:c r="E199" s="59"/>
-    </x:row>
-    <x:row r="200">
-      <x:c r="E200" s="59"/>
-    </x:row>
-    <x:row r="201">
-      <x:c r="E201" s="59"/>
-    </x:row>
-    <x:row r="202">
-      <x:c r="E202" s="59"/>
-    </x:row>
-    <x:row r="203">
-      <x:c r="E203" s="59"/>
-    </x:row>
-    <x:row r="204">
-      <x:c r="E204" s="59"/>
-    </x:row>
-    <x:row r="205">
-      <x:c r="E205" s="59"/>
-    </x:row>
-    <x:row r="206">
-      <x:c r="E206" s="59"/>
-    </x:row>
-    <x:row r="207">
-      <x:c r="E207" s="59"/>
-    </x:row>
-    <x:row r="208">
-      <x:c r="E208" s="59"/>
-    </x:row>
-    <x:row r="209">
-      <x:c r="E209" s="59"/>
-    </x:row>
-    <x:row r="210">
-      <x:c r="E210" s="59"/>
-    </x:row>
-    <x:row r="211">
-      <x:c r="E211" s="59"/>
-    </x:row>
-    <x:row r="212">
-      <x:c r="E212" s="59"/>
-    </x:row>
-    <x:row r="213">
-      <x:c r="E213" s="59"/>
-    </x:row>
-    <x:row r="214">
-      <x:c r="E214" s="59"/>
-    </x:row>
-    <x:row r="215">
-      <x:c r="E215" s="59"/>
-    </x:row>
-    <x:row r="216">
-      <x:c r="E216" s="59"/>
-    </x:row>
-    <x:row r="217">
-      <x:c r="E217" s="59"/>
-    </x:row>
-    <x:row r="218">
-      <x:c r="E218" s="59"/>
-    </x:row>
-    <x:row r="219">
-      <x:c r="E219" s="59"/>
-    </x:row>
-    <x:row r="220">
-      <x:c r="E220" s="59"/>
-    </x:row>
-    <x:row r="221">
-      <x:c r="E221" s="59"/>
-    </x:row>
-    <x:row r="222">
-      <x:c r="E222" s="59"/>
-    </x:row>
-    <x:row r="223">
-      <x:c r="E223" s="59"/>
-    </x:row>
-    <x:row r="224">
-      <x:c r="E224" s="59"/>
-    </x:row>
-    <x:row r="225">
-      <x:c r="E225" s="59"/>
-    </x:row>
-    <x:row r="226">
-      <x:c r="E226" s="59"/>
-    </x:row>
-    <x:row r="227">
-      <x:c r="E227" s="59"/>
-    </x:row>
-    <x:row r="228">
-      <x:c r="E228" s="59"/>
-    </x:row>
-    <x:row r="229">
-      <x:c r="E229" s="59"/>
-    </x:row>
-    <x:row r="230">
-      <x:c r="E230" s="59"/>
-    </x:row>
-    <x:row r="231">
-      <x:c r="E231" s="59"/>
-    </x:row>
-    <x:row r="232">
-      <x:c r="E232" s="59"/>
-    </x:row>
-    <x:row r="233">
-      <x:c r="E233" s="59"/>
-    </x:row>
-    <x:row r="234">
-      <x:c r="E234" s="59"/>
-    </x:row>
-    <x:row r="235">
-      <x:c r="E235" s="59"/>
-    </x:row>
-    <x:row r="236">
-      <x:c r="E236" s="59"/>
-    </x:row>
-    <x:row r="237">
-      <x:c r="E237" s="59"/>
-    </x:row>
-    <x:row r="238">
-      <x:c r="E238" s="59"/>
-    </x:row>
-    <x:row r="239">
-      <x:c r="E239" s="59"/>
-    </x:row>
-    <x:row r="240">
-      <x:c r="E240" s="59"/>
-    </x:row>
-    <x:row r="241">
-      <x:c r="E241" s="59"/>
-    </x:row>
-    <x:row r="242">
-      <x:c r="E242" s="59"/>
-    </x:row>
-    <x:row r="243">
-      <x:c r="E243" s="59"/>
-    </x:row>
-    <x:row r="244">
-      <x:c r="E244" s="59"/>
-    </x:row>
-    <x:row r="245">
-      <x:c r="E245" s="59"/>
-    </x:row>
-    <x:row r="246">
-      <x:c r="E246" s="59"/>
-    </x:row>
-    <x:row r="247">
-      <x:c r="E247" s="59"/>
-    </x:row>
-    <x:row r="248">
-      <x:c r="E248" s="59"/>
-    </x:row>
-    <x:row r="249">
-      <x:c r="E249" s="59"/>
-    </x:row>
-    <x:row r="250">
-      <x:c r="E250" s="59"/>
-    </x:row>
-    <x:row r="251">
-      <x:c r="E251" s="59"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="E252" s="59"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="E253" s="59"/>
-    </x:row>
-    <x:row r="254">
-      <x:c r="E254" s="59"/>
-    </x:row>
-    <x:row r="255">
-      <x:c r="E255" s="59"/>
-    </x:row>
-    <x:row r="256">
-      <x:c r="E256" s="59"/>
-    </x:row>
-    <x:row r="257">
-      <x:c r="E257" s="59"/>
-    </x:row>
-    <x:row r="258">
-      <x:c r="E258" s="59"/>
-    </x:row>
-    <x:row r="259">
-      <x:c r="E259" s="59"/>
-    </x:row>
-    <x:row r="260">
-      <x:c r="E260" s="59"/>
-    </x:row>
-    <x:row r="261">
-      <x:c r="E261" s="59"/>
-    </x:row>
-    <x:row r="262">
-      <x:c r="E262" s="59"/>
-    </x:row>
-    <x:row r="263">
-      <x:c r="E263" s="59"/>
-    </x:row>
-    <x:row r="264">
-      <x:c r="E264" s="59"/>
-    </x:row>
-    <x:row r="265">
-      <x:c r="E265" s="59"/>
-    </x:row>
-    <x:row r="266">
-      <x:c r="E266" s="59"/>
-    </x:row>
-    <x:row r="267">
-      <x:c r="E267" s="59"/>
-    </x:row>
-    <x:row r="268">
-      <x:c r="E268" s="59"/>
-    </x:row>
-    <x:row r="269">
-      <x:c r="E269" s="59"/>
-    </x:row>
-    <x:row r="270">
-      <x:c r="E270" s="59"/>
-    </x:row>
-    <x:row r="271">
-      <x:c r="E271" s="59"/>
-    </x:row>
-    <x:row r="272">
-      <x:c r="E272" s="59"/>
-    </x:row>
-    <x:row r="273">
-      <x:c r="E273" s="59"/>
-    </x:row>
-    <x:row r="274">
-      <x:c r="E274" s="59"/>
-    </x:row>
-    <x:row r="275">
-      <x:c r="E275" s="59"/>
-    </x:row>
-    <x:row r="276">
-      <x:c r="E276" s="59"/>
-    </x:row>
-    <x:row r="277">
-      <x:c r="E277" s="59"/>
-    </x:row>
-    <x:row r="278">
-      <x:c r="E278" s="59"/>
-    </x:row>
-    <x:row r="279">
-      <x:c r="E279" s="59"/>
-    </x:row>
-    <x:row r="280">
-      <x:c r="E280" s="59"/>
-    </x:row>
-    <x:row r="281">
-      <x:c r="E281" s="59"/>
-    </x:row>
-    <x:row r="282">
-      <x:c r="E282" s="59"/>
-    </x:row>
-    <x:row r="283">
-      <x:c r="E283" s="59"/>
-    </x:row>
-    <x:row r="284">
-      <x:c r="E284" s="59"/>
-    </x:row>
-    <x:row r="285">
-      <x:c r="E285" s="59"/>
-    </x:row>
-    <x:row r="286">
-      <x:c r="E286" s="59"/>
-    </x:row>
-    <x:row r="287">
-      <x:c r="E287" s="59"/>
-    </x:row>
-    <x:row r="288">
-      <x:c r="E288" s="59"/>
-    </x:row>
-    <x:row r="289">
-      <x:c r="E289" s="59"/>
-    </x:row>
-    <x:row r="290">
-      <x:c r="E290" s="59"/>
-    </x:row>
-    <x:row r="291">
-      <x:c r="E291" s="59"/>
-    </x:row>
-    <x:row r="292">
-      <x:c r="E292" s="59"/>
-    </x:row>
-    <x:row r="293">
-      <x:c r="E293" s="59"/>
-    </x:row>
-    <x:row r="294">
-      <x:c r="E294" s="59"/>
-    </x:row>
-    <x:row r="295">
-      <x:c r="E295" s="59"/>
-    </x:row>
-    <x:row r="296">
-      <x:c r="E296" s="59"/>
-    </x:row>
-    <x:row r="297">
-      <x:c r="E297" s="59"/>
-    </x:row>
-    <x:row r="298">
-      <x:c r="E298" s="59"/>
-    </x:row>
-    <x:row r="299">
-      <x:c r="E299" s="59"/>
-    </x:row>
-    <x:row r="300">
-      <x:c r="E300" s="59"/>
-    </x:row>
-    <x:row r="301">
-      <x:c r="E301" s="59"/>
-    </x:row>
-    <x:row r="302">
-      <x:c r="E302" s="59"/>
-    </x:row>
-    <x:row r="303">
-      <x:c r="E303" s="59"/>
-    </x:row>
-    <x:row r="304">
-      <x:c r="E304" s="59"/>
-    </x:row>
-    <x:row r="305">
-      <x:c r="E305" s="59"/>
-    </x:row>
-    <x:row r="306">
-      <x:c r="E306" s="59"/>
-    </x:row>
-    <x:row r="307">
-      <x:c r="E307" s="59"/>
-    </x:row>
-    <x:row r="308">
-      <x:c r="E308" s="59"/>
-    </x:row>
-    <x:row r="309">
-      <x:c r="E309" s="59"/>
-    </x:row>
-    <x:row r="310">
-      <x:c r="E310" s="59"/>
-    </x:row>
-    <x:row r="311">
-      <x:c r="E311" s="59"/>
-    </x:row>
-    <x:row r="312">
-      <x:c r="E312" s="59"/>
-    </x:row>
-    <x:row r="313">
-      <x:c r="E313" s="59"/>
-    </x:row>
-    <x:row r="314">
-      <x:c r="E314" s="59"/>
-    </x:row>
-    <x:row r="315">
-      <x:c r="E315" s="59"/>
-    </x:row>
-    <x:row r="316">
-      <x:c r="E316" s="59"/>
-    </x:row>
-    <x:row r="317">
-      <x:c r="E317" s="59"/>
-    </x:row>
-    <x:row r="318">
-      <x:c r="E318" s="59"/>
-    </x:row>
-    <x:row r="319">
-      <x:c r="E319" s="59"/>
-    </x:row>
-    <x:row r="320">
-      <x:c r="E320" s="59"/>
-    </x:row>
-    <x:row r="321">
-      <x:c r="E321" s="59"/>
-    </x:row>
-    <x:row r="322">
-      <x:c r="E322" s="59"/>
-    </x:row>
-    <x:row r="323">
-      <x:c r="E323" s="59"/>
-    </x:row>
-    <x:row r="324">
-      <x:c r="E324" s="59"/>
-    </x:row>
-    <x:row r="325">
-      <x:c r="E325" s="59"/>
-    </x:row>
-    <x:row r="326">
-      <x:c r="E326" s="59"/>
-    </x:row>
-    <x:row r="327">
-      <x:c r="E327" s="59"/>
-    </x:row>
-    <x:row r="328">
-      <x:c r="E328" s="59"/>
-    </x:row>
-    <x:row r="329">
-      <x:c r="E329" s="59"/>
-    </x:row>
-    <x:row r="330">
-      <x:c r="E330" s="59"/>
-    </x:row>
-    <x:row r="331">
-      <x:c r="E331" s="59"/>
-    </x:row>
-    <x:row r="332">
-      <x:c r="E332" s="59"/>
-    </x:row>
-    <x:row r="333">
-      <x:c r="E333" s="59"/>
-    </x:row>
-    <x:row r="334">
-      <x:c r="E334" s="59"/>
-    </x:row>
-    <x:row r="335">
-      <x:c r="E335" s="59"/>
-    </x:row>
-    <x:row r="336">
-      <x:c r="E336" s="59"/>
-    </x:row>
-    <x:row r="337">
-      <x:c r="E337" s="59"/>
-    </x:row>
-    <x:row r="338">
-      <x:c r="E338" s="59"/>
-    </x:row>
-    <x:row r="339">
-      <x:c r="E339" s="59"/>
-    </x:row>
-    <x:row r="340">
-      <x:c r="E340" s="59"/>
-    </x:row>
-    <x:row r="341">
-      <x:c r="E341" s="59"/>
-    </x:row>
-    <x:row r="342">
-      <x:c r="E342" s="59"/>
-    </x:row>
-    <x:row r="343">
-      <x:c r="E343" s="59"/>
-    </x:row>
-    <x:row r="344">
-      <x:c r="E344" s="59"/>
-    </x:row>
-    <x:row r="345">
-      <x:c r="E345" s="59"/>
-    </x:row>
-    <x:row r="346">
-      <x:c r="E346" s="59"/>
-    </x:row>
-    <x:row r="347">
-      <x:c r="E347" s="59"/>
-    </x:row>
-    <x:row r="348">
-      <x:c r="E348" s="59"/>
-    </x:row>
-    <x:row r="349">
-      <x:c r="E349" s="59"/>
-    </x:row>
-    <x:row r="350">
-      <x:c r="E350" s="59"/>
-    </x:row>
-    <x:row r="351">
-      <x:c r="E351" s="59"/>
-    </x:row>
-    <x:row r="352">
-      <x:c r="E352" s="59"/>
-    </x:row>
-    <x:row r="353">
-      <x:c r="E353" s="59"/>
-    </x:row>
-    <x:row r="354">
-      <x:c r="E354" s="59"/>
-    </x:row>
-    <x:row r="355">
-      <x:c r="E355" s="59"/>
-    </x:row>
-    <x:row r="356">
-      <x:c r="E356" s="59"/>
-    </x:row>
-    <x:row r="357">
-      <x:c r="E357" s="59"/>
-    </x:row>
-    <x:row r="358">
-      <x:c r="E358" s="59"/>
-    </x:row>
-    <x:row r="359">
-      <x:c r="E359" s="59"/>
-    </x:row>
-    <x:row r="360">
-      <x:c r="E360" s="59"/>
-    </x:row>
-    <x:row r="361">
-      <x:c r="E361" s="59"/>
-    </x:row>
-    <x:row r="362">
-      <x:c r="E362" s="59"/>
-    </x:row>
-    <x:row r="363">
-      <x:c r="E363" s="59"/>
-    </x:row>
-    <x:row r="364">
-      <x:c r="E364" s="59"/>
-    </x:row>
-    <x:row r="365">
-      <x:c r="E365" s="59"/>
-    </x:row>
-    <x:row r="366">
-      <x:c r="E366" s="59"/>
-    </x:row>
-    <x:row r="367">
-      <x:c r="E367" s="59"/>
-    </x:row>
-    <x:row r="368">
-      <x:c r="E368" s="59"/>
-    </x:row>
-    <x:row r="369">
-      <x:c r="E369" s="59"/>
-    </x:row>
-    <x:row r="370">
-      <x:c r="E370" s="59"/>
-    </x:row>
-    <x:row r="371">
-      <x:c r="E371" s="59"/>
-    </x:row>
-    <x:row r="372">
-      <x:c r="E372" s="59"/>
-    </x:row>
-    <x:row r="373">
-      <x:c r="E373" s="59"/>
-    </x:row>
-    <x:row r="374">
-      <x:c r="E374" s="59"/>
-    </x:row>
-    <x:row r="375">
-      <x:c r="E375" s="59"/>
-    </x:row>
-    <x:row r="376">
-      <x:c r="E376" s="59"/>
-    </x:row>
-    <x:row r="377">
-      <x:c r="E377" s="59"/>
-    </x:row>
-    <x:row r="378">
-      <x:c r="E378" s="59"/>
-    </x:row>
-    <x:row r="379">
-      <x:c r="E379" s="59"/>
-    </x:row>
-    <x:row r="380">
-      <x:c r="E380" s="59"/>
-    </x:row>
-    <x:row r="381">
-      <x:c r="E381" s="59"/>
-    </x:row>
-    <x:row r="382">
-      <x:c r="E382" s="59"/>
-    </x:row>
-    <x:row r="383">
-      <x:c r="E383" s="59"/>
-    </x:row>
-    <x:row r="384">
-      <x:c r="E384" s="59"/>
-    </x:row>
-    <x:row r="385">
-      <x:c r="E385" s="59"/>
-    </x:row>
-    <x:row r="386">
-      <x:c r="E386" s="59"/>
-    </x:row>
-    <x:row r="387">
-      <x:c r="E387" s="59"/>
-    </x:row>
-    <x:row r="388">
-      <x:c r="E388" s="59"/>
-    </x:row>
-    <x:row r="389">
-      <x:c r="E389" s="59"/>
-    </x:row>
-    <x:row r="390">
-      <x:c r="E390" s="59"/>
-    </x:row>
-    <x:row r="391">
-      <x:c r="E391" s="59"/>
-    </x:row>
-    <x:row r="392">
-      <x:c r="E392" s="59"/>
-    </x:row>
-    <x:row r="393">
-      <x:c r="E393" s="59"/>
-    </x:row>
-    <x:row r="394">
-      <x:c r="E394" s="59"/>
-    </x:row>
-    <x:row r="395">
-      <x:c r="E395" s="59"/>
-    </x:row>
-    <x:row r="396">
-      <x:c r="E396" s="59"/>
-    </x:row>
-    <x:row r="397">
-      <x:c r="E397" s="59"/>
-    </x:row>
-    <x:row r="398">
-      <x:c r="E398" s="59"/>
-    </x:row>
-    <x:row r="399">
-      <x:c r="E399" s="59"/>
-    </x:row>
-    <x:row r="400">
-      <x:c r="E400" s="59"/>
-    </x:row>
-    <x:row r="401">
-      <x:c r="E401" s="59"/>
-    </x:row>
-    <x:row r="402">
-      <x:c r="E402" s="59"/>
-    </x:row>
-    <x:row r="403">
-      <x:c r="E403" s="59"/>
-    </x:row>
-    <x:row r="404">
-      <x:c r="E404" s="59"/>
-    </x:row>
-    <x:row r="405">
-      <x:c r="E405" s="59"/>
-    </x:row>
-    <x:row r="406">
-      <x:c r="E406" s="59"/>
-    </x:row>
-    <x:row r="407">
-      <x:c r="E407" s="59"/>
-    </x:row>
-    <x:row r="408">
-      <x:c r="E408" s="59"/>
-    </x:row>
-    <x:row r="409">
-      <x:c r="E409" s="59"/>
-    </x:row>
-    <x:row r="410">
-      <x:c r="E410" s="59"/>
-    </x:row>
-    <x:row r="411">
-      <x:c r="E411" s="59"/>
-    </x:row>
-    <x:row r="412">
-      <x:c r="E412" s="59"/>
-    </x:row>
-    <x:row r="413">
-      <x:c r="E413" s="59"/>
-    </x:row>
-    <x:row r="414">
-      <x:c r="E414" s="59"/>
-    </x:row>
-    <x:row r="415">
-      <x:c r="E415" s="59"/>
-    </x:row>
-    <x:row r="416">
-      <x:c r="E416" s="59"/>
-    </x:row>
-    <x:row r="417">
-      <x:c r="E417" s="59"/>
-    </x:row>
-    <x:row r="418">
-      <x:c r="E418" s="59"/>
-    </x:row>
-    <x:row r="419">
-      <x:c r="E419" s="59"/>
-    </x:row>
-    <x:row r="420">
-      <x:c r="E420" s="59"/>
-    </x:row>
-    <x:row r="421">
-      <x:c r="E421" s="59"/>
-    </x:row>
-    <x:row r="422">
-      <x:c r="E422" s="59"/>
-    </x:row>
-    <x:row r="423">
-      <x:c r="E423" s="59"/>
-    </x:row>
-    <x:row r="424">
-      <x:c r="E424" s="59"/>
-    </x:row>
-    <x:row r="425">
-      <x:c r="E425" s="59"/>
-    </x:row>
-    <x:row r="426">
-      <x:c r="E426" s="59"/>
-    </x:row>
-    <x:row r="427">
-      <x:c r="E427" s="59"/>
-    </x:row>
-    <x:row r="428">
-      <x:c r="E428" s="59"/>
-    </x:row>
-    <x:row r="429">
-      <x:c r="E429" s="59"/>
-    </x:row>
-    <x:row r="430">
-      <x:c r="E430" s="59"/>
-    </x:row>
-    <x:row r="431">
-      <x:c r="E431" s="59"/>
-    </x:row>
-    <x:row r="432">
-      <x:c r="E432" s="59"/>
-    </x:row>
-    <x:row r="433">
-      <x:c r="E433" s="59"/>
-    </x:row>
-    <x:row r="434">
-      <x:c r="E434" s="59"/>
-    </x:row>
-    <x:row r="435">
-      <x:c r="E435" s="59"/>
-    </x:row>
-    <x:row r="436">
-      <x:c r="E436" s="59"/>
-    </x:row>
-    <x:row r="437">
-      <x:c r="E437" s="59"/>
-    </x:row>
-    <x:row r="438">
-      <x:c r="E438" s="59"/>
-    </x:row>
-    <x:row r="439">
-      <x:c r="E439" s="59"/>
-    </x:row>
-    <x:row r="440">
-      <x:c r="E440" s="59"/>
-    </x:row>
-    <x:row r="441">
-      <x:c r="E441" s="59"/>
-    </x:row>
-    <x:row r="442">
-      <x:c r="E442" s="59"/>
-    </x:row>
-    <x:row r="443">
-      <x:c r="E443" s="59"/>
-    </x:row>
-    <x:row r="444">
-      <x:c r="E444" s="59"/>
-    </x:row>
-    <x:row r="445">
-      <x:c r="E445" s="59"/>
-    </x:row>
-    <x:row r="446">
-      <x:c r="E446" s="59"/>
-    </x:row>
-    <x:row r="447">
-      <x:c r="E447" s="59"/>
-    </x:row>
-    <x:row r="448">
-      <x:c r="E448" s="59"/>
-    </x:row>
-    <x:row r="449">
-      <x:c r="E449" s="59"/>
-    </x:row>
-    <x:row r="450">
-      <x:c r="E450" s="59"/>
-    </x:row>
-    <x:row r="451">
-      <x:c r="E451" s="59"/>
-    </x:row>
-    <x:row r="452">
-      <x:c r="E452" s="59"/>
-    </x:row>
-    <x:row r="453">
-      <x:c r="E453" s="59"/>
-    </x:row>
-    <x:row r="454">
-      <x:c r="E454" s="59"/>
-    </x:row>
-    <x:row r="455">
-      <x:c r="E455" s="59"/>
-    </x:row>
-    <x:row r="456">
-      <x:c r="E456" s="59"/>
-    </x:row>
-    <x:row r="457">
-      <x:c r="E457" s="59"/>
-    </x:row>
-    <x:row r="458">
-      <x:c r="E458" s="59"/>
-    </x:row>
-    <x:row r="459">
-      <x:c r="E459" s="59"/>
-    </x:row>
-    <x:row r="460">
-      <x:c r="E460" s="59"/>
-    </x:row>
-    <x:row r="461">
-      <x:c r="E461" s="59"/>
-    </x:row>
-    <x:row r="462">
-      <x:c r="E462" s="59"/>
-    </x:row>
-    <x:row r="463">
-      <x:c r="E463" s="59"/>
-    </x:row>
-    <x:row r="464">
-      <x:c r="E464" s="59"/>
-    </x:row>
-    <x:row r="465">
-      <x:c r="E465" s="59"/>
-    </x:row>
-    <x:row r="466">
-      <x:c r="E466" s="59"/>
-    </x:row>
-    <x:row r="467">
-      <x:c r="E467" s="59"/>
-    </x:row>
-    <x:row r="468">
-      <x:c r="E468" s="59"/>
-    </x:row>
-    <x:row r="469">
-      <x:c r="E469" s="59"/>
-    </x:row>
-    <x:row r="470">
-      <x:c r="E470" s="59"/>
-    </x:row>
-    <x:row r="471">
-      <x:c r="E471" s="59"/>
-    </x:row>
-    <x:row r="472">
-      <x:c r="E472" s="59"/>
-    </x:row>
-    <x:row r="473">
-      <x:c r="E473" s="59"/>
-    </x:row>
-    <x:row r="474">
-      <x:c r="E474" s="59"/>
-    </x:row>
-    <x:row r="475">
-      <x:c r="E475" s="59"/>
-    </x:row>
-    <x:row r="476">
-      <x:c r="E476" s="59"/>
-    </x:row>
-    <x:row r="477">
-      <x:c r="E477" s="59"/>
-    </x:row>
-    <x:row r="478">
-      <x:c r="E478" s="59"/>
-    </x:row>
-    <x:row r="479">
-      <x:c r="E479" s="59"/>
-    </x:row>
-    <x:row r="480">
-      <x:c r="E480" s="59"/>
-    </x:row>
-    <x:row r="481">
-      <x:c r="E481" s="59"/>
-    </x:row>
-    <x:row r="482">
-      <x:c r="E482" s="59"/>
-    </x:row>
-    <x:row r="483">
-      <x:c r="E483" s="59"/>
-    </x:row>
-    <x:row r="484">
-      <x:c r="E484" s="59"/>
-    </x:row>
-    <x:row r="485">
-      <x:c r="E485" s="59"/>
-    </x:row>
-    <x:row r="486">
-      <x:c r="E486" s="59"/>
-    </x:row>
-    <x:row r="487">
-      <x:c r="E487" s="59"/>
-    </x:row>
-    <x:row r="488">
-      <x:c r="E488" s="59"/>
-    </x:row>
-    <x:row r="489">
-      <x:c r="E489" s="59"/>
-    </x:row>
-    <x:row r="490">
-      <x:c r="E490" s="59"/>
-    </x:row>
-    <x:row r="491">
-      <x:c r="E491" s="59"/>
-    </x:row>
-    <x:row r="492">
-      <x:c r="E492" s="59"/>
-    </x:row>
-    <x:row r="493">
-      <x:c r="E493" s="59"/>
-    </x:row>
-    <x:row r="494">
-      <x:c r="E494" s="59"/>
-    </x:row>
-    <x:row r="495">
-      <x:c r="E495" s="59"/>
-    </x:row>
-    <x:row r="496">
-      <x:c r="E496" s="59"/>
-    </x:row>
-    <x:row r="497">
-      <x:c r="E497" s="59"/>
-    </x:row>
-    <x:row r="498">
-      <x:c r="E498" s="59"/>
-    </x:row>
-    <x:row r="499">
-      <x:c r="E499" s="59"/>
-    </x:row>
-    <x:row r="500">
-      <x:c r="E500" s="59"/>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F2:F500">
-      <x:formula1>"0,1"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4475,7 +2942,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4625,7 +3092,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4680,7 +3147,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4774,61 +3241,6 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="52" t="str">
-        <x:v>scope_tenant_code</x:v>
-      </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>connection_tenant_code</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>connection_system_code</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>connection_code</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>zone_code</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>object_schema</x:v>
-      </x:c>
-      <x:c r="G1" s="57" t="str">
-        <x:v>is_active</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="47"/>
-      <x:c r="B2" s="48"/>
-      <x:c r="C2" s="48"/>
-      <x:c r="D2" s="48"/>
-      <x:c r="E2" s="48"/>
-      <x:c r="F2" s="48"/>
-      <x:c r="G2" s="49"/>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="G2:G500">
-      <x:formula1>"0,1"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
     <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
@@ -4885,7 +3297,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4930,63 +3342,67 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="19.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="52" t="str">
+      <x:c r="A1" s="62" t="str">
         <x:v>tenant_code</x:v>
       </x:c>
-      <x:c r="B1" s="52" t="str">
+      <x:c r="B1" s="62" t="str">
+        <x:v>source_tenant_code</x:v>
+      </x:c>
+      <x:c r="C1" s="62" t="str">
         <x:v>system_code</x:v>
       </x:c>
-      <x:c r="C1" s="52" t="str">
+      <x:c r="D1" s="62" t="str">
         <x:v>connection_code</x:v>
       </x:c>
-      <x:c r="D1" s="52" t="str">
+      <x:c r="E1" s="62" t="str">
         <x:v>object_schema</x:v>
       </x:c>
-      <x:c r="E1" s="52" t="str">
+      <x:c r="F1" s="62" t="str">
         <x:v>object_name</x:v>
       </x:c>
-      <x:c r="F1" s="57" t="str">
+      <x:c r="G1" s="63" t="str">
         <x:v>fc_object_schema</x:v>
       </x:c>
-      <x:c r="G1" s="57" t="str">
+      <x:c r="H1" s="63" t="str">
         <x:v>fc_object_name</x:v>
       </x:c>
-      <x:c r="H1" s="57" t="str">
+      <x:c r="I1" s="63" t="str">
         <x:v>object_transformation</x:v>
       </x:c>
-      <x:c r="I1" s="57" t="str">
+      <x:c r="J1" s="63" t="str">
         <x:v>object_description</x:v>
       </x:c>
-      <x:c r="J1" s="57" t="str">
+      <x:c r="K1" s="63" t="str">
         <x:v>batch_attribute_name</x:v>
       </x:c>
-      <x:c r="K1" s="52" t="str">
+      <x:c r="L1" s="62" t="str">
         <x:v>object_type_code</x:v>
       </x:c>
-      <x:c r="L1" s="52" t="str">
+      <x:c r="M1" s="62" t="str">
         <x:v>zone_code</x:v>
       </x:c>
-      <x:c r="M1" s="57" t="str">
+      <x:c r="N1" s="67" t="str">
         <x:v>is_active</x:v>
       </x:c>
     </x:row>
@@ -5004,6 +3420,7 @@
       <x:c r="K2" s="48"/>
       <x:c r="L2" s="48"/>
       <x:c r="M2" s="49"/>
+      <x:c r="N2"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -5015,7 +3432,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5156,7 +3573,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5231,7 +3648,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5316,7 +3733,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5367,4 +3784,1548 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="52" t="str">
+        <x:v>tenant_code</x:v>
+      </x:c>
+      <x:c r="B1" s="52" t="str">
+        <x:v>system_code</x:v>
+      </x:c>
+      <x:c r="C1" s="52" t="str">
+        <x:v>member_group_name</x:v>
+      </x:c>
+      <x:c r="D1" s="57" t="str">
+        <x:v>member_group_description</x:v>
+      </x:c>
+      <x:c r="E1" s="57" t="str">
+        <x:v>member_group_initial_load_date</x:v>
+      </x:c>
+      <x:c r="F1" s="57" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="47"/>
+      <x:c r="B2" s="48"/>
+      <x:c r="C2" s="48"/>
+      <x:c r="D2" s="48"/>
+      <x:c r="E2" s="58"/>
+      <x:c r="F2" s="49"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="E3" s="59"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="E4" s="59"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="E5" s="59"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="E6" s="59"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="E7" s="59"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="E8" s="59"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="E9" s="59"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="E10" s="59"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="E11" s="59"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="E12" s="59"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="E13" s="59"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="E14" s="59"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="E15" s="59"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="E16" s="59"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="E17" s="59"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="E18" s="59"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="E19" s="59"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="E20" s="59"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="E21" s="59"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="E22" s="59"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="E23" s="59"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="E24" s="59"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="E25" s="59"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="E26" s="59"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="E27" s="59"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="E28" s="59"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="E29" s="59"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="E30" s="59"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="E31" s="59"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="E32" s="59"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="E33" s="59"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="E34" s="59"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="E35" s="59"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="E36" s="59"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="E37" s="59"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="E38" s="59"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="E39" s="59"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="E40" s="59"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="E41" s="59"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="E42" s="59"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="E43" s="59"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="E44" s="59"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="E45" s="59"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="E46" s="59"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="E47" s="59"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="E48" s="59"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="E49" s="59"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="E50" s="59"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="E51" s="59"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="E52" s="59"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="E53" s="59"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="E54" s="59"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="E55" s="59"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="E56" s="59"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="E57" s="59"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="E58" s="59"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="E59" s="59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="E60" s="59"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="E61" s="59"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="E62" s="59"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="E63" s="59"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="E64" s="59"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="E65" s="59"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="E66" s="59"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="E67" s="59"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="E68" s="59"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="E69" s="59"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="E70" s="59"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="E71" s="59"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="E72" s="59"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="E73" s="59"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="E74" s="59"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="E75" s="59"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="E76" s="59"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="E77" s="59"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="E78" s="59"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="E79" s="59"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="E80" s="59"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="E81" s="59"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="E82" s="59"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="E83" s="59"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="E84" s="59"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="E85" s="59"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="E86" s="59"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="E87" s="59"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="E88" s="59"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="E89" s="59"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="E90" s="59"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="E91" s="59"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="E92" s="59"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="E93" s="59"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="E94" s="59"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="E95" s="59"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="E96" s="59"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="E97" s="59"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="E98" s="59"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="E99" s="59"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="E100" s="59"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="E101" s="59"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="E102" s="59"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="E103" s="59"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="E104" s="59"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="E105" s="59"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="E106" s="59"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="E107" s="59"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="E108" s="59"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="E109" s="59"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="E110" s="59"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="E111" s="59"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="E112" s="59"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="E113" s="59"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="E114" s="59"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="E115" s="59"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="E116" s="59"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="E117" s="59"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="E118" s="59"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="E119" s="59"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="E120" s="59"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="E121" s="59"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="E122" s="59"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="E123" s="59"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="E124" s="59"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="E125" s="59"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="E126" s="59"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="E127" s="59"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="E128" s="59"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="E129" s="59"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="E130" s="59"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="E131" s="59"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="E132" s="59"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="E133" s="59"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="E134" s="59"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="E135" s="59"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="E136" s="59"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="E137" s="59"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="E138" s="59"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="E139" s="59"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="E140" s="59"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="E141" s="59"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="E142" s="59"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="E143" s="59"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="E144" s="59"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="E145" s="59"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="E146" s="59"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="E147" s="59"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="E148" s="59"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="E149" s="59"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="E150" s="59"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="E151" s="59"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="E152" s="59"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="E153" s="59"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="E154" s="59"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="E155" s="59"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="E156" s="59"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="E157" s="59"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="E158" s="59"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="E159" s="59"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="E160" s="59"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="E161" s="59"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="E162" s="59"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="E163" s="59"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="E164" s="59"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="E165" s="59"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="E166" s="59"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="E167" s="59"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="E168" s="59"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="E169" s="59"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="E170" s="59"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="E171" s="59"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="E172" s="59"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="E173" s="59"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="E174" s="59"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="E175" s="59"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="E176" s="59"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="E177" s="59"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="E178" s="59"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="E179" s="59"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="E180" s="59"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="E181" s="59"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="E182" s="59"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="E183" s="59"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="E184" s="59"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="E185" s="59"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="E186" s="59"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="E187" s="59"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="E188" s="59"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="E189" s="59"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="E190" s="59"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="E191" s="59"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="E192" s="59"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="E193" s="59"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="E194" s="59"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="E195" s="59"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="E196" s="59"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="E197" s="59"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="E198" s="59"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="E199" s="59"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="E200" s="59"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="E201" s="59"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="E202" s="59"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="E203" s="59"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="E204" s="59"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="E205" s="59"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="E206" s="59"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="E207" s="59"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="E208" s="59"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="E209" s="59"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="E210" s="59"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="E211" s="59"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="E212" s="59"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="E213" s="59"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="E214" s="59"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="E215" s="59"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="E216" s="59"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="E217" s="59"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="E218" s="59"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="E219" s="59"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="E220" s="59"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="E221" s="59"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="E222" s="59"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="E223" s="59"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="E224" s="59"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="E225" s="59"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="E226" s="59"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="E227" s="59"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="E228" s="59"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="E229" s="59"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="E230" s="59"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="E231" s="59"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="E232" s="59"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="E233" s="59"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="E234" s="59"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="E235" s="59"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="E236" s="59"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="E237" s="59"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="E238" s="59"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="E239" s="59"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="E240" s="59"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="E241" s="59"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="E242" s="59"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="E243" s="59"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="E244" s="59"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="E245" s="59"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="E246" s="59"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="E247" s="59"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="E248" s="59"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="E249" s="59"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="E250" s="59"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="E251" s="59"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="E252" s="59"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="E253" s="59"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="E254" s="59"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="E255" s="59"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="E256" s="59"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="E257" s="59"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="E258" s="59"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="E259" s="59"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="E260" s="59"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="E261" s="59"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="E262" s="59"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="E263" s="59"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="E264" s="59"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="E265" s="59"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="E266" s="59"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="E267" s="59"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="E268" s="59"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="E269" s="59"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="E270" s="59"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="E271" s="59"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="E272" s="59"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="E273" s="59"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="E274" s="59"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="E275" s="59"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="E276" s="59"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="E277" s="59"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="E278" s="59"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="E279" s="59"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="E280" s="59"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="E281" s="59"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="E282" s="59"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="E283" s="59"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="E284" s="59"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="E285" s="59"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="E286" s="59"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="E287" s="59"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="E288" s="59"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="E289" s="59"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="E290" s="59"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="E291" s="59"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="E292" s="59"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="E293" s="59"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="E294" s="59"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="E295" s="59"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="E296" s="59"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="E297" s="59"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="E298" s="59"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="E299" s="59"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="E300" s="59"/>
+    </x:row>
+    <x:row r="301">
+      <x:c r="E301" s="59"/>
+    </x:row>
+    <x:row r="302">
+      <x:c r="E302" s="59"/>
+    </x:row>
+    <x:row r="303">
+      <x:c r="E303" s="59"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="E304" s="59"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="E305" s="59"/>
+    </x:row>
+    <x:row r="306">
+      <x:c r="E306" s="59"/>
+    </x:row>
+    <x:row r="307">
+      <x:c r="E307" s="59"/>
+    </x:row>
+    <x:row r="308">
+      <x:c r="E308" s="59"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="E309" s="59"/>
+    </x:row>
+    <x:row r="310">
+      <x:c r="E310" s="59"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="E311" s="59"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="E312" s="59"/>
+    </x:row>
+    <x:row r="313">
+      <x:c r="E313" s="59"/>
+    </x:row>
+    <x:row r="314">
+      <x:c r="E314" s="59"/>
+    </x:row>
+    <x:row r="315">
+      <x:c r="E315" s="59"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="E316" s="59"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="E317" s="59"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="E318" s="59"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="E319" s="59"/>
+    </x:row>
+    <x:row r="320">
+      <x:c r="E320" s="59"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="E321" s="59"/>
+    </x:row>
+    <x:row r="322">
+      <x:c r="E322" s="59"/>
+    </x:row>
+    <x:row r="323">
+      <x:c r="E323" s="59"/>
+    </x:row>
+    <x:row r="324">
+      <x:c r="E324" s="59"/>
+    </x:row>
+    <x:row r="325">
+      <x:c r="E325" s="59"/>
+    </x:row>
+    <x:row r="326">
+      <x:c r="E326" s="59"/>
+    </x:row>
+    <x:row r="327">
+      <x:c r="E327" s="59"/>
+    </x:row>
+    <x:row r="328">
+      <x:c r="E328" s="59"/>
+    </x:row>
+    <x:row r="329">
+      <x:c r="E329" s="59"/>
+    </x:row>
+    <x:row r="330">
+      <x:c r="E330" s="59"/>
+    </x:row>
+    <x:row r="331">
+      <x:c r="E331" s="59"/>
+    </x:row>
+    <x:row r="332">
+      <x:c r="E332" s="59"/>
+    </x:row>
+    <x:row r="333">
+      <x:c r="E333" s="59"/>
+    </x:row>
+    <x:row r="334">
+      <x:c r="E334" s="59"/>
+    </x:row>
+    <x:row r="335">
+      <x:c r="E335" s="59"/>
+    </x:row>
+    <x:row r="336">
+      <x:c r="E336" s="59"/>
+    </x:row>
+    <x:row r="337">
+      <x:c r="E337" s="59"/>
+    </x:row>
+    <x:row r="338">
+      <x:c r="E338" s="59"/>
+    </x:row>
+    <x:row r="339">
+      <x:c r="E339" s="59"/>
+    </x:row>
+    <x:row r="340">
+      <x:c r="E340" s="59"/>
+    </x:row>
+    <x:row r="341">
+      <x:c r="E341" s="59"/>
+    </x:row>
+    <x:row r="342">
+      <x:c r="E342" s="59"/>
+    </x:row>
+    <x:row r="343">
+      <x:c r="E343" s="59"/>
+    </x:row>
+    <x:row r="344">
+      <x:c r="E344" s="59"/>
+    </x:row>
+    <x:row r="345">
+      <x:c r="E345" s="59"/>
+    </x:row>
+    <x:row r="346">
+      <x:c r="E346" s="59"/>
+    </x:row>
+    <x:row r="347">
+      <x:c r="E347" s="59"/>
+    </x:row>
+    <x:row r="348">
+      <x:c r="E348" s="59"/>
+    </x:row>
+    <x:row r="349">
+      <x:c r="E349" s="59"/>
+    </x:row>
+    <x:row r="350">
+      <x:c r="E350" s="59"/>
+    </x:row>
+    <x:row r="351">
+      <x:c r="E351" s="59"/>
+    </x:row>
+    <x:row r="352">
+      <x:c r="E352" s="59"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="E353" s="59"/>
+    </x:row>
+    <x:row r="354">
+      <x:c r="E354" s="59"/>
+    </x:row>
+    <x:row r="355">
+      <x:c r="E355" s="59"/>
+    </x:row>
+    <x:row r="356">
+      <x:c r="E356" s="59"/>
+    </x:row>
+    <x:row r="357">
+      <x:c r="E357" s="59"/>
+    </x:row>
+    <x:row r="358">
+      <x:c r="E358" s="59"/>
+    </x:row>
+    <x:row r="359">
+      <x:c r="E359" s="59"/>
+    </x:row>
+    <x:row r="360">
+      <x:c r="E360" s="59"/>
+    </x:row>
+    <x:row r="361">
+      <x:c r="E361" s="59"/>
+    </x:row>
+    <x:row r="362">
+      <x:c r="E362" s="59"/>
+    </x:row>
+    <x:row r="363">
+      <x:c r="E363" s="59"/>
+    </x:row>
+    <x:row r="364">
+      <x:c r="E364" s="59"/>
+    </x:row>
+    <x:row r="365">
+      <x:c r="E365" s="59"/>
+    </x:row>
+    <x:row r="366">
+      <x:c r="E366" s="59"/>
+    </x:row>
+    <x:row r="367">
+      <x:c r="E367" s="59"/>
+    </x:row>
+    <x:row r="368">
+      <x:c r="E368" s="59"/>
+    </x:row>
+    <x:row r="369">
+      <x:c r="E369" s="59"/>
+    </x:row>
+    <x:row r="370">
+      <x:c r="E370" s="59"/>
+    </x:row>
+    <x:row r="371">
+      <x:c r="E371" s="59"/>
+    </x:row>
+    <x:row r="372">
+      <x:c r="E372" s="59"/>
+    </x:row>
+    <x:row r="373">
+      <x:c r="E373" s="59"/>
+    </x:row>
+    <x:row r="374">
+      <x:c r="E374" s="59"/>
+    </x:row>
+    <x:row r="375">
+      <x:c r="E375" s="59"/>
+    </x:row>
+    <x:row r="376">
+      <x:c r="E376" s="59"/>
+    </x:row>
+    <x:row r="377">
+      <x:c r="E377" s="59"/>
+    </x:row>
+    <x:row r="378">
+      <x:c r="E378" s="59"/>
+    </x:row>
+    <x:row r="379">
+      <x:c r="E379" s="59"/>
+    </x:row>
+    <x:row r="380">
+      <x:c r="E380" s="59"/>
+    </x:row>
+    <x:row r="381">
+      <x:c r="E381" s="59"/>
+    </x:row>
+    <x:row r="382">
+      <x:c r="E382" s="59"/>
+    </x:row>
+    <x:row r="383">
+      <x:c r="E383" s="59"/>
+    </x:row>
+    <x:row r="384">
+      <x:c r="E384" s="59"/>
+    </x:row>
+    <x:row r="385">
+      <x:c r="E385" s="59"/>
+    </x:row>
+    <x:row r="386">
+      <x:c r="E386" s="59"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="E387" s="59"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="E388" s="59"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="E389" s="59"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="E390" s="59"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="E391" s="59"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="E392" s="59"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="E393" s="59"/>
+    </x:row>
+    <x:row r="394">
+      <x:c r="E394" s="59"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="E395" s="59"/>
+    </x:row>
+    <x:row r="396">
+      <x:c r="E396" s="59"/>
+    </x:row>
+    <x:row r="397">
+      <x:c r="E397" s="59"/>
+    </x:row>
+    <x:row r="398">
+      <x:c r="E398" s="59"/>
+    </x:row>
+    <x:row r="399">
+      <x:c r="E399" s="59"/>
+    </x:row>
+    <x:row r="400">
+      <x:c r="E400" s="59"/>
+    </x:row>
+    <x:row r="401">
+      <x:c r="E401" s="59"/>
+    </x:row>
+    <x:row r="402">
+      <x:c r="E402" s="59"/>
+    </x:row>
+    <x:row r="403">
+      <x:c r="E403" s="59"/>
+    </x:row>
+    <x:row r="404">
+      <x:c r="E404" s="59"/>
+    </x:row>
+    <x:row r="405">
+      <x:c r="E405" s="59"/>
+    </x:row>
+    <x:row r="406">
+      <x:c r="E406" s="59"/>
+    </x:row>
+    <x:row r="407">
+      <x:c r="E407" s="59"/>
+    </x:row>
+    <x:row r="408">
+      <x:c r="E408" s="59"/>
+    </x:row>
+    <x:row r="409">
+      <x:c r="E409" s="59"/>
+    </x:row>
+    <x:row r="410">
+      <x:c r="E410" s="59"/>
+    </x:row>
+    <x:row r="411">
+      <x:c r="E411" s="59"/>
+    </x:row>
+    <x:row r="412">
+      <x:c r="E412" s="59"/>
+    </x:row>
+    <x:row r="413">
+      <x:c r="E413" s="59"/>
+    </x:row>
+    <x:row r="414">
+      <x:c r="E414" s="59"/>
+    </x:row>
+    <x:row r="415">
+      <x:c r="E415" s="59"/>
+    </x:row>
+    <x:row r="416">
+      <x:c r="E416" s="59"/>
+    </x:row>
+    <x:row r="417">
+      <x:c r="E417" s="59"/>
+    </x:row>
+    <x:row r="418">
+      <x:c r="E418" s="59"/>
+    </x:row>
+    <x:row r="419">
+      <x:c r="E419" s="59"/>
+    </x:row>
+    <x:row r="420">
+      <x:c r="E420" s="59"/>
+    </x:row>
+    <x:row r="421">
+      <x:c r="E421" s="59"/>
+    </x:row>
+    <x:row r="422">
+      <x:c r="E422" s="59"/>
+    </x:row>
+    <x:row r="423">
+      <x:c r="E423" s="59"/>
+    </x:row>
+    <x:row r="424">
+      <x:c r="E424" s="59"/>
+    </x:row>
+    <x:row r="425">
+      <x:c r="E425" s="59"/>
+    </x:row>
+    <x:row r="426">
+      <x:c r="E426" s="59"/>
+    </x:row>
+    <x:row r="427">
+      <x:c r="E427" s="59"/>
+    </x:row>
+    <x:row r="428">
+      <x:c r="E428" s="59"/>
+    </x:row>
+    <x:row r="429">
+      <x:c r="E429" s="59"/>
+    </x:row>
+    <x:row r="430">
+      <x:c r="E430" s="59"/>
+    </x:row>
+    <x:row r="431">
+      <x:c r="E431" s="59"/>
+    </x:row>
+    <x:row r="432">
+      <x:c r="E432" s="59"/>
+    </x:row>
+    <x:row r="433">
+      <x:c r="E433" s="59"/>
+    </x:row>
+    <x:row r="434">
+      <x:c r="E434" s="59"/>
+    </x:row>
+    <x:row r="435">
+      <x:c r="E435" s="59"/>
+    </x:row>
+    <x:row r="436">
+      <x:c r="E436" s="59"/>
+    </x:row>
+    <x:row r="437">
+      <x:c r="E437" s="59"/>
+    </x:row>
+    <x:row r="438">
+      <x:c r="E438" s="59"/>
+    </x:row>
+    <x:row r="439">
+      <x:c r="E439" s="59"/>
+    </x:row>
+    <x:row r="440">
+      <x:c r="E440" s="59"/>
+    </x:row>
+    <x:row r="441">
+      <x:c r="E441" s="59"/>
+    </x:row>
+    <x:row r="442">
+      <x:c r="E442" s="59"/>
+    </x:row>
+    <x:row r="443">
+      <x:c r="E443" s="59"/>
+    </x:row>
+    <x:row r="444">
+      <x:c r="E444" s="59"/>
+    </x:row>
+    <x:row r="445">
+      <x:c r="E445" s="59"/>
+    </x:row>
+    <x:row r="446">
+      <x:c r="E446" s="59"/>
+    </x:row>
+    <x:row r="447">
+      <x:c r="E447" s="59"/>
+    </x:row>
+    <x:row r="448">
+      <x:c r="E448" s="59"/>
+    </x:row>
+    <x:row r="449">
+      <x:c r="E449" s="59"/>
+    </x:row>
+    <x:row r="450">
+      <x:c r="E450" s="59"/>
+    </x:row>
+    <x:row r="451">
+      <x:c r="E451" s="59"/>
+    </x:row>
+    <x:row r="452">
+      <x:c r="E452" s="59"/>
+    </x:row>
+    <x:row r="453">
+      <x:c r="E453" s="59"/>
+    </x:row>
+    <x:row r="454">
+      <x:c r="E454" s="59"/>
+    </x:row>
+    <x:row r="455">
+      <x:c r="E455" s="59"/>
+    </x:row>
+    <x:row r="456">
+      <x:c r="E456" s="59"/>
+    </x:row>
+    <x:row r="457">
+      <x:c r="E457" s="59"/>
+    </x:row>
+    <x:row r="458">
+      <x:c r="E458" s="59"/>
+    </x:row>
+    <x:row r="459">
+      <x:c r="E459" s="59"/>
+    </x:row>
+    <x:row r="460">
+      <x:c r="E460" s="59"/>
+    </x:row>
+    <x:row r="461">
+      <x:c r="E461" s="59"/>
+    </x:row>
+    <x:row r="462">
+      <x:c r="E462" s="59"/>
+    </x:row>
+    <x:row r="463">
+      <x:c r="E463" s="59"/>
+    </x:row>
+    <x:row r="464">
+      <x:c r="E464" s="59"/>
+    </x:row>
+    <x:row r="465">
+      <x:c r="E465" s="59"/>
+    </x:row>
+    <x:row r="466">
+      <x:c r="E466" s="59"/>
+    </x:row>
+    <x:row r="467">
+      <x:c r="E467" s="59"/>
+    </x:row>
+    <x:row r="468">
+      <x:c r="E468" s="59"/>
+    </x:row>
+    <x:row r="469">
+      <x:c r="E469" s="59"/>
+    </x:row>
+    <x:row r="470">
+      <x:c r="E470" s="59"/>
+    </x:row>
+    <x:row r="471">
+      <x:c r="E471" s="59"/>
+    </x:row>
+    <x:row r="472">
+      <x:c r="E472" s="59"/>
+    </x:row>
+    <x:row r="473">
+      <x:c r="E473" s="59"/>
+    </x:row>
+    <x:row r="474">
+      <x:c r="E474" s="59"/>
+    </x:row>
+    <x:row r="475">
+      <x:c r="E475" s="59"/>
+    </x:row>
+    <x:row r="476">
+      <x:c r="E476" s="59"/>
+    </x:row>
+    <x:row r="477">
+      <x:c r="E477" s="59"/>
+    </x:row>
+    <x:row r="478">
+      <x:c r="E478" s="59"/>
+    </x:row>
+    <x:row r="479">
+      <x:c r="E479" s="59"/>
+    </x:row>
+    <x:row r="480">
+      <x:c r="E480" s="59"/>
+    </x:row>
+    <x:row r="481">
+      <x:c r="E481" s="59"/>
+    </x:row>
+    <x:row r="482">
+      <x:c r="E482" s="59"/>
+    </x:row>
+    <x:row r="483">
+      <x:c r="E483" s="59"/>
+    </x:row>
+    <x:row r="484">
+      <x:c r="E484" s="59"/>
+    </x:row>
+    <x:row r="485">
+      <x:c r="E485" s="59"/>
+    </x:row>
+    <x:row r="486">
+      <x:c r="E486" s="59"/>
+    </x:row>
+    <x:row r="487">
+      <x:c r="E487" s="59"/>
+    </x:row>
+    <x:row r="488">
+      <x:c r="E488" s="59"/>
+    </x:row>
+    <x:row r="489">
+      <x:c r="E489" s="59"/>
+    </x:row>
+    <x:row r="490">
+      <x:c r="E490" s="59"/>
+    </x:row>
+    <x:row r="491">
+      <x:c r="E491" s="59"/>
+    </x:row>
+    <x:row r="492">
+      <x:c r="E492" s="59"/>
+    </x:row>
+    <x:row r="493">
+      <x:c r="E493" s="59"/>
+    </x:row>
+    <x:row r="494">
+      <x:c r="E494" s="59"/>
+    </x:row>
+    <x:row r="495">
+      <x:c r="E495" s="59"/>
+    </x:row>
+    <x:row r="496">
+      <x:c r="E496" s="59"/>
+    </x:row>
+    <x:row r="497">
+      <x:c r="E497" s="59"/>
+    </x:row>
+    <x:row r="498">
+      <x:c r="E498" s="59"/>
+    </x:row>
+    <x:row r="499">
+      <x:c r="E499" s="59"/>
+    </x:row>
+    <x:row r="500">
+      <x:c r="E500" s="59"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="F2:F500">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>